--- a/system_development/BOM-v0.3-cart.xlsx
+++ b/system_development/BOM-v0.3-cart.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mk103\Documents\GitHub\flowthrough-water-quality-monitoring-system\system_development\Moultrie\v0.3\cart\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mk103\Documents\GitHub\flowthrough-water-quality-monitoring-system\system_development\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A93A822-D71C-411F-B407-FE7936545BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ACCD291-A7B6-43B8-8282-284D3F8D52D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
   <si>
     <t>Total Cost</t>
   </si>
@@ -180,6 +180,15 @@
   </si>
   <si>
     <t>https://www.grainger.com/product/HDPE-Sheet-0-25-in-Thick-1ZAL8</t>
+  </si>
+  <si>
+    <t>Relay Module</t>
+  </si>
+  <si>
+    <t>12V 1 Channel Relay Module with Optocoupler Isolation High/Low Level Trigger</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/166286100101?chn=ps&amp;_trkparms=ispr%3D1&amp;amdata=enc%3A1AOsTJtXlRhetE-2aOOWbuQ28&amp;norover=1&amp;mkrid=711-173151-913341-5&amp;mkcid=2&amp;mkscid=101&amp;itemid=166286100101&amp;targetid=2321110923541&amp;device=c&amp;mktype=pla&amp;googleloc=9010433&amp;poi=&amp;campaignid=21400684010&amp;mkgroupid=173029508068&amp;rlsatarget=pla-2321110923541&amp;abcId=9448486&amp;merchantid=101645423&amp;gad_source=1&amp;gad_campaignid=21400684010&amp;gbraid=0AAAAAD_QDh9jbBqHDR9n1PvmvLpKOq0ju&amp;gclid=CjwKCAjw857RBhAgEiwAI-1yKL9q29fCTuM_gBzzlJIO6D3D1VhA_jDtgUe760kKVIEhhQraJM75choCOgsQAvD_BwE</t>
   </si>
 </sst>
 </file>
@@ -908,12 +917,25 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="3"/>
+      <c r="A14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="2">
+        <v>5</v>
+      </c>
+      <c r="D14" s="6">
+        <v>1.22</v>
+      </c>
+      <c r="E14" s="6">
+        <f>C14*D14</f>
+        <v>6.1</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -980,7 +1002,7 @@
       </c>
       <c r="E21" s="8">
         <f>SUM(E2:E20)</f>
-        <v>572.83000000000004</v>
+        <v>578.93000000000006</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1147,7 +1169,7 @@
       </c>
       <c r="E42" s="6">
         <f>SUM(E2:E41)</f>
-        <v>1145.6600000000001</v>
+        <v>1157.8600000000001</v>
       </c>
     </row>
   </sheetData>
